--- a/chumonsho_A4.xlsx
+++ b/chumonsho_A4.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahono\Documents\株式会社若林商店\発注書書き方マニュアル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E6D3B7-D6B4-4504-AA37-CDADD53B1DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4304754-0D74-4023-9DBD-A76C69692526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
   <si>
     <t>記入日</t>
   </si>
@@ -63,24 +63,9 @@
     <t>豚こま</t>
   </si>
   <si>
-    <t>豚こま（脂なし）</t>
-  </si>
-  <si>
-    <t>豚ももこま</t>
-  </si>
-  <si>
-    <t>豚ももこま（脂なし）</t>
-  </si>
-  <si>
-    <t>角切り</t>
-  </si>
-  <si>
     <t>豚ひき</t>
   </si>
   <si>
-    <t>豚ひき（脂なし）</t>
-  </si>
-  <si>
     <t>豚バラ</t>
   </si>
   <si>
@@ -90,9 +75,6 @@
     <t>豚ロース</t>
   </si>
   <si>
-    <t>豚ロース（脂なし）</t>
-  </si>
-  <si>
     <t>豚ヒレ</t>
   </si>
   <si>
@@ -108,54 +90,21 @@
     <t>鶏ムネこま</t>
   </si>
   <si>
-    <t>鶏ムネこま（皮なし）</t>
-  </si>
-  <si>
     <t>鶏モモこま</t>
   </si>
   <si>
-    <t>鶏モモこま（皮なし）</t>
-  </si>
-  <si>
-    <t>鶏ムネ（g指定切り身）</t>
-  </si>
-  <si>
-    <t>鶏ムネ（g指定切り身）（皮なし）</t>
-  </si>
-  <si>
-    <t>鶏モモ（g指定切り身）</t>
-  </si>
-  <si>
-    <t>鶏モモ（g指定切り身）（皮なし）</t>
-  </si>
-  <si>
     <t>鶏ムネひき</t>
   </si>
   <si>
-    <t>鶏ムネひき（皮なし）</t>
-  </si>
-  <si>
     <t>鶏モモひき</t>
   </si>
   <si>
-    <t>鶏モモひき（皮なし）</t>
-  </si>
-  <si>
     <t>鶏ササミ</t>
   </si>
   <si>
     <t>鶏ササミひき</t>
   </si>
   <si>
-    <t>鶏手羽元</t>
-  </si>
-  <si>
-    <t>鶏手羽先</t>
-  </si>
-  <si>
-    <t>鶏骨付きモモ</t>
-  </si>
-  <si>
     <t>鶏レバー</t>
   </si>
   <si>
@@ -165,37 +114,7 @@
     <t>【牛肉】</t>
   </si>
   <si>
-    <t>牛スライス</t>
-  </si>
-  <si>
-    <t>牛こま（脂なし）</t>
-  </si>
-  <si>
     <t>牛ひき</t>
-  </si>
-  <si>
-    <t>牛ひき（脂なし）</t>
-  </si>
-  <si>
-    <t>合いびき</t>
-  </si>
-  <si>
-    <t>【ハム類】</t>
-  </si>
-  <si>
-    <t>ロースハム</t>
-  </si>
-  <si>
-    <t>ポークハム</t>
-  </si>
-  <si>
-    <t>ベーコン</t>
-  </si>
-  <si>
-    <t>ウインナー</t>
-  </si>
-  <si>
-    <t>フランクフルト</t>
   </si>
   <si>
     <t>リストにないものも自由記入可</t>
@@ -228,21 +147,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>千切り</t>
-    <rPh sb="0" eb="2">
-      <t>センギ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>g*</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>g×</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>備考一覧</t>
     <rPh sb="2" eb="4">
       <t>イチラン</t>
@@ -266,40 +170,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>色紙切り</t>
-    <rPh sb="0" eb="2">
-      <t>シキシ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ギ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>短冊切り</t>
-    <rPh sb="0" eb="2">
-      <t>タンザク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ギ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>極小こま</t>
-    <rPh sb="0" eb="2">
-      <t>ゴクショウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>本</t>
-    <rPh sb="0" eb="1">
-      <t>ホン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>いつもお世話になっています。</t>
     <rPh sb="4" eb="6">
       <t>セワ</t>
@@ -307,19 +177,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>発注書ひな形です、ご自由に編集してお使いください。</t>
-    <rPh sb="0" eb="3">
-      <t>ハッチュウショ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジユウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ご不明点はお気軽にお問い合わせください。</t>
     <rPh sb="1" eb="4">
       <t>フメイテン</t>
@@ -382,27 +239,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>g*　開き</t>
-    <rPh sb="3" eb="4">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>g×　開き</t>
-    <rPh sb="3" eb="4">
-      <t>ヒラ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>*=×の意味です</t>
-    <rPh sb="4" eb="6">
-      <t>イミ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>*と×は同じ意味です、お好きな表記で構いません。g指定切りに関してはドロップダウンリストを使用せず直接キーボードでの入力が簡単です。</t>
     <rPh sb="4" eb="5">
       <t>オナ</t>
@@ -493,31 +329,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>特殊な切り方指定がある場合のみ備考欄にて指定をお願いいたします。</t>
-    <rPh sb="0" eb="2">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>カタシテイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ビコウラン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>ネガ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>説明</t>
     <rPh sb="0" eb="2">
       <t>セツメイ</t>
@@ -525,58 +336,9 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>枚</t>
-    <rPh sb="0" eb="1">
-      <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>商品名一覧（灰色枠内編集OKです）</t>
     <rPh sb="6" eb="12">
       <t>ハイイロワクナイヘンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>30g*45　このような簡易表記でOKです　＝30g×45枚　</t>
-    <rPh sb="12" eb="16">
-      <t>カンイヒョウキ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>マイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ソフトサラミ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>こま肉の大きさに関しましては基本的には当社規定の保育園様向けの小さめサイズで納品しています。</t>
-    <rPh sb="2" eb="3">
-      <t>ニク</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="14" eb="17">
-      <t>キホンテキ</t>
-    </rPh>
-    <rPh sb="19" eb="23">
-      <t>トウシャキテイ</t>
-    </rPh>
-    <rPh sb="24" eb="29">
-      <t>ホイクエンサマム</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>チイ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ノウヒン</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -603,28 +365,160 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>株式会社若林商店宛　FAX03-3637-8501</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>豚こま(脂なし)</t>
+  </si>
+  <si>
+    <t>豚モモこま</t>
+  </si>
+  <si>
+    <t>豚モモこま(脂なし)</t>
+  </si>
+  <si>
+    <t>豚ひき(脂なし)</t>
+  </si>
+  <si>
     <t>豚モモひき</t>
+  </si>
+  <si>
+    <t>豚モモひき(脂なし)</t>
+  </si>
+  <si>
+    <t>豚ロース(脂なし)</t>
+  </si>
+  <si>
+    <t>鶏ムネ(g指定切り身)</t>
+  </si>
+  <si>
+    <t>鶏ムネ(g指定切り身)(皮なし)</t>
+  </si>
+  <si>
+    <t>鶏モモ(g指定切り身)</t>
+  </si>
+  <si>
+    <t>鶏モモ(g指定切り)(皮なし)</t>
+  </si>
+  <si>
+    <t>鶏ムネこま(皮なし)</t>
+  </si>
+  <si>
+    <t>鶏モモこま(皮なし)</t>
+  </si>
+  <si>
+    <t>鶏ムネひき(皮なし)</t>
+  </si>
+  <si>
+    <t>鶏モモひき(皮なし)</t>
+  </si>
+  <si>
+    <t>鶏テバモト</t>
+  </si>
+  <si>
+    <t>鶏テバサキ</t>
+  </si>
+  <si>
+    <t>鶏骨付モモ</t>
+  </si>
+  <si>
+    <t>【ハム類・皮】</t>
+  </si>
+  <si>
+    <t>ベーコン(乳卵なし)</t>
+  </si>
+  <si>
+    <t>ポークハム(乳卵なし)</t>
+  </si>
+  <si>
+    <t>ソフトサラミ(乳卵なし)</t>
+  </si>
+  <si>
+    <t>ロースハム(乳卵なし)</t>
+  </si>
+  <si>
+    <t>ウインナー(乳卵なし)</t>
+  </si>
+  <si>
+    <t>フランクフルト(乳卵なし)</t>
+  </si>
+  <si>
+    <t>シューマイの皮</t>
+  </si>
+  <si>
+    <t>ギョウザの皮</t>
+  </si>
+  <si>
+    <t>ワンタンの皮</t>
+  </si>
+  <si>
+    <t>牛こま</t>
+  </si>
+  <si>
+    <t>牛こま(脂なし)</t>
+  </si>
+  <si>
+    <t>牛ひき(脂なし)</t>
+  </si>
+  <si>
+    <t>あいびき</t>
+  </si>
+  <si>
+    <t>角</t>
+  </si>
+  <si>
+    <t>大きさを付けて（例 1cm角）</t>
+  </si>
+  <si>
+    <t>色紙</t>
+  </si>
+  <si>
+    <t>大きさを付けて（例 7mm色紙）</t>
+  </si>
+  <si>
+    <t>短冊</t>
+  </si>
+  <si>
+    <t>ハム・ベーコンは書かなければ短冊</t>
+  </si>
+  <si>
+    <t>千切り</t>
+  </si>
+  <si>
+    <t>g*</t>
+  </si>
+  <si>
+    <t>30g*45　このような簡易表記でOKです　＝30g×45枚（*=×の意味です）</t>
+  </si>
+  <si>
+    <t>g*　開き</t>
+  </si>
+  <si>
+    <t>g×</t>
+  </si>
+  <si>
+    <t>g×　開き</t>
+  </si>
+  <si>
+    <t>本</t>
+  </si>
+  <si>
+    <t>ササミなどの本数発注は重量未記入でOKです</t>
+  </si>
+  <si>
+    <t>枚</t>
+  </si>
+  <si>
+    <t>注文書のひな形です。ご自由に編集してお使いください。</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>豚モモひき（脂なし）</t>
+    <t>こま肉の大きさは、基本的に当社規定の保育園様・学校様向けの小さめのサイズで納品しています。</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>ササミなどの本数発注は重量未記入でOKです</t>
-    <rPh sb="6" eb="8">
-      <t>ホンスウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ハッチュウ</t>
-    </rPh>
-    <rPh sb="11" eb="16">
-      <t>ジュウリョウミキニュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>株式会社若林商店宛　FAX03-3637-8501</t>
+    <t>特別な切り方の指定がある場合のみ、備考欄でご指定ください（切り方の言葉は「切り方と商品名の一覧表」をご覧ください）。</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -811,7 +705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -892,15 +786,16 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1226,33 +1121,33 @@
     <row r="1" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
       <c r="B1" s="8" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="11">
         <f ca="1">TODAY()</f>
-        <v>46210</v>
+        <v>46311</v>
       </c>
       <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" ht="39.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="32"/>
+      <c r="A3" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="33"/>
       <c r="C3" s="31" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D3" s="31"/>
       <c r="E3" s="9"/>
@@ -1265,22 +1160,22 @@
     </row>
     <row r="5" spans="1:5" s="17" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="48.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>2</v>
@@ -1296,9 +1191,7 @@
     <row r="7" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="29">
-        <v>5</v>
-      </c>
+      <c r="C7" s="29"/>
       <c r="D7" s="24"/>
       <c r="E7" s="9"/>
     </row>
@@ -1507,12 +1400,6 @@
           </x14:formula1>
           <xm:sqref>A7:A22</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{73FE1B98-1FF4-4D6C-B029-1EF587C54496}">
-          <x14:formula1>
-            <xm:f>日付リスト!$C$2:$C$14</xm:f>
-          </x14:formula1>
-          <xm:sqref>B1</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{CE5A62FE-65B6-4044-A9B9-83750C803BE4}">
           <x14:formula1>
             <xm:f>備考一覧!$A$2:$A$100</xm:f>
@@ -1531,11 +1418,17 @@
           </x14:formula1>
           <xm:sqref>B23:B30</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{15A4637B-DE76-412C-B59E-7C8E061B78AB}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{00E0BD47-2B48-451F-937F-9D6C4342CFB4}">
           <x14:formula1>
-            <xm:f>商品名一覧!$A$2:$A$50</xm:f>
+            <xm:f>商品名一覧!$A$2:$A$53</xm:f>
           </x14:formula1>
           <xm:sqref>B7:B22</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{528F5B7E-8B6B-4E74-8BAD-677D27ED0033}">
+          <x14:formula1>
+            <xm:f>日付リスト!$C$2:$C$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1554,10 +1447,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1572,247 +1465,253 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="4"/>
+      <c r="A51" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="4"/>
+      <c r="A52" s="4" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="4"/>
+      <c r="A53" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
@@ -1958,94 +1857,98 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36E415E-C943-43E4-AE41-011A0B49F18B}">
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="40.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
@@ -2314,47 +2217,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2374,310 +2277,334 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+0)=MONTH(注文書!$B$1),注文書!$B$1+0,""),TODAY()+0)</f>
-        <v>46210</v>
+        <v>46311</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+1)=MONTH(注文書!$B$1),注文書!$B$1+1,""),TODAY()+1)</f>
-        <v>46211</v>
+        <v>46312</v>
       </c>
       <c r="C3" s="6">
-        <v>46174</v>
+        <v>46173.625</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+2)=MONTH(注文書!$B$1),注文書!$B$1+2,""),TODAY()+2)</f>
-        <v>46212</v>
+        <v>46313</v>
       </c>
       <c r="C4" s="6">
-        <v>46204</v>
+        <v>46203.625</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+3)=MONTH(注文書!$B$1),注文書!$B$1+3,""),TODAY()+3)</f>
-        <v>46213</v>
+        <v>46314</v>
       </c>
       <c r="C5" s="6">
-        <v>46235</v>
+        <v>46234.625</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+4)=MONTH(注文書!$B$1),注文書!$B$1+4,""),TODAY()+4)</f>
-        <v>46214</v>
+        <v>46315</v>
       </c>
       <c r="C6" s="6">
-        <v>46266</v>
+        <v>46265.625</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+5)=MONTH(注文書!$B$1),注文書!$B$1+5,""),TODAY()+5)</f>
-        <v>46215</v>
+        <v>46316</v>
       </c>
       <c r="C7" s="6">
-        <v>46296</v>
+        <v>46295.625</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+6)=MONTH(注文書!$B$1),注文書!$B$1+6,""),TODAY()+6)</f>
-        <v>46216</v>
+        <v>46317</v>
       </c>
       <c r="C8" s="6">
-        <v>46327</v>
+        <v>46326.625</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+7)=MONTH(注文書!$B$1),注文書!$B$1+7,""),TODAY()+7)</f>
-        <v>46217</v>
+        <v>46318</v>
       </c>
       <c r="C9" s="6">
-        <v>46357</v>
+        <v>46356.625</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+8)=MONTH(注文書!$B$1),注文書!$B$1+8,""),TODAY()+8)</f>
-        <v>46218</v>
+        <v>46319</v>
       </c>
       <c r="C10" s="6">
-        <v>46388</v>
+        <v>46387.625</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+9)=MONTH(注文書!$B$1),注文書!$B$1+9,""),TODAY()+9)</f>
-        <v>46219</v>
+        <v>46320</v>
       </c>
       <c r="C11" s="6">
-        <v>46419</v>
+        <v>46418.625</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+10)=MONTH(注文書!$B$1),注文書!$B$1+10,""),TODAY()+10)</f>
-        <v>46220</v>
+        <v>46321</v>
       </c>
       <c r="C12" s="6">
-        <v>46447</v>
+        <v>46446.625</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+11)=MONTH(注文書!$B$1),注文書!$B$1+11,""),TODAY()+11)</f>
-        <v>46221</v>
+        <v>46322</v>
       </c>
       <c r="C13" s="6">
-        <v>46478</v>
+        <v>46477.625</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+12)=MONTH(注文書!$B$1),注文書!$B$1+12,""),TODAY()+12)</f>
-        <v>46222</v>
+        <v>46323</v>
       </c>
       <c r="C14" s="6">
-        <v>46508</v>
+        <v>46507.625</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+13)=MONTH(注文書!$B$1),注文書!$B$1+13,""),TODAY()+13)</f>
-        <v>46223</v>
+        <v>46324</v>
+      </c>
+      <c r="C15" s="35">
+        <v>46538.625</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+14)=MONTH(注文書!$B$1),注文書!$B$1+14,""),TODAY()+14)</f>
-        <v>46224</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46325</v>
+      </c>
+      <c r="C16" s="35">
+        <v>46568.625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+15)=MONTH(注文書!$B$1),注文書!$B$1+15,""),TODAY()+15)</f>
-        <v>46225</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46326</v>
+      </c>
+      <c r="C17" s="35">
+        <v>46599.625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+16)=MONTH(注文書!$B$1),注文書!$B$1+16,""),TODAY()+16)</f>
-        <v>46226</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46327</v>
+      </c>
+      <c r="C18" s="35">
+        <v>46630.625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+17)=MONTH(注文書!$B$1),注文書!$B$1+17,""),TODAY()+17)</f>
-        <v>46227</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46328</v>
+      </c>
+      <c r="C19" s="35">
+        <v>46660.625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+18)=MONTH(注文書!$B$1),注文書!$B$1+18,""),TODAY()+18)</f>
-        <v>46228</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46329</v>
+      </c>
+      <c r="C20" s="35">
+        <v>46691.625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+19)=MONTH(注文書!$B$1),注文書!$B$1+19,""),TODAY()+19)</f>
-        <v>46229</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46330</v>
+      </c>
+      <c r="C21" s="35">
+        <v>46721.625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+20)=MONTH(注文書!$B$1),注文書!$B$1+20,""),TODAY()+20)</f>
-        <v>46230</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46331</v>
+      </c>
+      <c r="C22" s="35">
+        <v>46752.625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+21)=MONTH(注文書!$B$1),注文書!$B$1+21,""),TODAY()+21)</f>
-        <v>46231</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+22)=MONTH(注文書!$B$1),注文書!$B$1+22,""),TODAY()+22)</f>
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+23)=MONTH(注文書!$B$1),注文書!$B$1+23,""),TODAY()+23)</f>
-        <v>46233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+24)=MONTH(注文書!$B$1),注文書!$B$1+24,""),TODAY()+24)</f>
-        <v>46234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+25)=MONTH(注文書!$B$1),注文書!$B$1+25,""),TODAY()+25)</f>
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+26)=MONTH(注文書!$B$1),注文書!$B$1+26,""),TODAY()+26)</f>
-        <v>46236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+27)=MONTH(注文書!$B$1),注文書!$B$1+27,""),TODAY()+27)</f>
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+28)=MONTH(注文書!$B$1),注文書!$B$1+28,""),TODAY()+28)</f>
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+29)=MONTH(注文書!$B$1),注文書!$B$1+29,""),TODAY()+29)</f>
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+30)=MONTH(注文書!$B$1),注文書!$B$1+30,""),TODAY()+30)</f>
-        <v>46240</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+31)=MONTH(注文書!$B$1),注文書!$B$1+31,""),TODAY()+31)</f>
-        <v>46241</v>
+        <v>46342</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+32)=MONTH(注文書!$B$1),注文書!$B$1+32,""),TODAY()+32)</f>
-        <v>46242</v>
+        <v>46343</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+33)=MONTH(注文書!$B$1),注文書!$B$1+33,""),TODAY()+33)</f>
-        <v>46243</v>
+        <v>46344</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+34)=MONTH(注文書!$B$1),注文書!$B$1+34,""),TODAY()+34)</f>
-        <v>46244</v>
+        <v>46345</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+35)=MONTH(注文書!$B$1),注文書!$B$1+35,""),TODAY()+35)</f>
-        <v>46245</v>
+        <v>46346</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+36)=MONTH(注文書!$B$1),注文書!$B$1+36,""),TODAY()+36)</f>
-        <v>46246</v>
+        <v>46347</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+37)=MONTH(注文書!$B$1),注文書!$B$1+37,""),TODAY()+37)</f>
-        <v>46247</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+38)=MONTH(注文書!$B$1),注文書!$B$1+38,""),TODAY()+38)</f>
-        <v>46248</v>
+        <v>46349</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+39)=MONTH(注文書!$B$1),注文書!$B$1+39,""),TODAY()+39)</f>
-        <v>46249</v>
+        <v>46350</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+40)=MONTH(注文書!$B$1),注文書!$B$1+40,""),TODAY()+40)</f>
-        <v>46250</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+41)=MONTH(注文書!$B$1),注文書!$B$1+41,""),TODAY()+41)</f>
-        <v>46251</v>
+        <v>46352</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+42)=MONTH(注文書!$B$1),注文書!$B$1+42,""),TODAY()+42)</f>
-        <v>46252</v>
+        <v>46353</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+43)=MONTH(注文書!$B$1),注文書!$B$1+43,""),TODAY()+43)</f>
-        <v>46253</v>
+        <v>46354</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+44)=MONTH(注文書!$B$1),注文書!$B$1+44,""),TODAY()+44)</f>
-        <v>46254</v>
+        <v>46355</v>
       </c>
     </row>
   </sheetData>

--- a/chumonsho_A4.xlsx
+++ b/chumonsho_A4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahono\Documents\株式会社若林商店\発注書書き方マニュアル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4304754-0D74-4023-9DBD-A76C69692526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C006461F-6E4E-49E6-88FB-834D13BA0695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="96">
   <si>
     <t>記入日</t>
   </si>
@@ -520,6 +520,15 @@
   <si>
     <t>特別な切り方の指定がある場合のみ、備考欄でご指定ください（切り方の言葉は「切り方と商品名の一覧表」をご覧ください）。</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>枚以上</t>
+  </si>
+  <si>
+    <t>シューマイ・ギョウザ・ワンタンの皮：数量は書かずに「160枚以上」のように。袋数は当社で計算します</t>
+  </si>
+  <si>
+    <t>シューマイ・ギョウザ・ワンタンの皮は、数量（kg）の欄は空けて、備考欄に「160枚以上」のように必要な枚数だけ書いてください。袋数は当社で計算します。</t>
   </si>
 </sst>
 </file>
@@ -782,6 +791,7 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
@@ -795,7 +805,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1133,29 +1142,29 @@
       <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" ht="39.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="31"/>
+      <c r="D3" s="32"/>
       <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5" ht="19.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="13"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5" s="17" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -1937,7 +1946,12 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
@@ -2248,6 +2262,11 @@
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
@@ -2396,7 +2415,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+13)=MONTH(注文書!$B$1),注文書!$B$1+13,""),TODAY()+13)</f>
         <v>46324</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="31">
         <v>46538.625</v>
       </c>
     </row>
@@ -2405,7 +2424,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+14)=MONTH(注文書!$B$1),注文書!$B$1+14,""),TODAY()+14)</f>
         <v>46325</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="31">
         <v>46568.625</v>
       </c>
     </row>
@@ -2414,7 +2433,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+15)=MONTH(注文書!$B$1),注文書!$B$1+15,""),TODAY()+15)</f>
         <v>46326</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="31">
         <v>46599.625</v>
       </c>
     </row>
@@ -2423,7 +2442,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+16)=MONTH(注文書!$B$1),注文書!$B$1+16,""),TODAY()+16)</f>
         <v>46327</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="31">
         <v>46630.625</v>
       </c>
     </row>
@@ -2432,7 +2451,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+17)=MONTH(注文書!$B$1),注文書!$B$1+17,""),TODAY()+17)</f>
         <v>46328</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="31">
         <v>46660.625</v>
       </c>
     </row>
@@ -2441,7 +2460,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+18)=MONTH(注文書!$B$1),注文書!$B$1+18,""),TODAY()+18)</f>
         <v>46329</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="31">
         <v>46691.625</v>
       </c>
     </row>
@@ -2450,7 +2469,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+19)=MONTH(注文書!$B$1),注文書!$B$1+19,""),TODAY()+19)</f>
         <v>46330</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="31">
         <v>46721.625</v>
       </c>
     </row>
@@ -2459,7 +2478,7 @@
         <f ca="1">IF(ISNUMBER(注文書!$B$1),IF(MONTH(注文書!$B$1+20)=MONTH(注文書!$B$1),注文書!$B$1+20,""),TODAY()+20)</f>
         <v>46331</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="31">
         <v>46752.625</v>
       </c>
     </row>

--- a/chumonsho_A4.xlsx
+++ b/chumonsho_A4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahono\Documents\株式会社若林商店\発注書書き方マニュアル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C006461F-6E4E-49E6-88FB-834D13BA0695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF23AB2-27F1-4A8A-8F75-6E2E5C925C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -170,165 +170,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>いつもお世話になっています。</t>
-    <rPh sb="4" eb="6">
-      <t>セワ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ご不明点はお気軽にお問い合わせください。</t>
-    <rPh sb="1" eb="4">
-      <t>フメイテン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キガル</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>g指定切りは備考欄に〇ｇ*△枚数と記入。可能であれば合計重量の記入も願います。未記入の場合枚数に合わせて合計重量計算いたします。</t>
-    <rPh sb="1" eb="4">
-      <t>シテイギ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>ビコウラン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>マイスウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>キニュウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="26" eb="30">
-      <t>ゴウケイジュウリョウ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>キニュウ</t>
-    </rPh>
-    <rPh sb="34" eb="35">
-      <t>ネガ</t>
-    </rPh>
-    <rPh sb="39" eb="42">
-      <t>ミキニュウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>マイスウ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="52" eb="56">
-      <t>ゴウケイジュウリョウ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ケイサン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>*と×は同じ意味です、お好きな表記で構いません。g指定切りに関してはドロップダウンリストを使用せず直接キーボードでの入力が簡単です。</t>
-    <rPh sb="4" eb="5">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イミ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヒョウキ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カマ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>ギ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>シヨウ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>チョクセツ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>カンタン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>商品名一覧と備考欄一覧の灰色背景枠内でご自由に表記登録が可能です、宛名を変更していただければ他社様宛の発注書にも転用可能です。</t>
-    <rPh sb="0" eb="5">
-      <t>ショウヒンメイイチラン</t>
-    </rPh>
-    <rPh sb="6" eb="11">
-      <t>ビコウランイチラン</t>
-    </rPh>
-    <rPh sb="12" eb="17">
-      <t>ハイイロハイケイワク</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ジユウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ヒョウキ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="28" eb="30">
-      <t>カノウ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>アテナ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="46" eb="50">
-      <t>タシャサマアテ</t>
-    </rPh>
-    <rPh sb="51" eb="54">
-      <t>ハッチュウショ</t>
-    </rPh>
-    <rPh sb="56" eb="60">
-      <t>テンヨウカノウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>株式会社若林商店　FAX：03-3637-8501</t>
-    <rPh sb="0" eb="8">
-      <t>カブシキガイシャワカバヤシショウテン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>説明</t>
     <rPh sb="0" eb="2">
       <t>セツメイ</t>
@@ -510,25 +351,40 @@
     <t>枚</t>
   </si>
   <si>
-    <t>注文書のひな形です。ご自由に編集してお使いください。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>こま肉の大きさは、基本的に当社規定の保育園様・学校様向けの小さめのサイズで納品しています。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>特別な切り方の指定がある場合のみ、備考欄でご指定ください（切り方の言葉は「切り方と商品名の一覧表」をご覧ください）。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>枚以上</t>
   </si>
   <si>
     <t>シューマイ・ギョウザ・ワンタンの皮：数量は書かずに「160枚以上」のように。袋数は当社で計算します</t>
   </si>
   <si>
-    <t>シューマイ・ギョウザ・ワンタンの皮は、数量（kg）の欄は空けて、備考欄に「160枚以上」のように必要な枚数だけ書いてください。袋数は当社で計算します。</t>
+    <t>使い方（3つだけ）</t>
+  </si>
+  <si>
+    <t>① はじめに「施設名記入」の所に、園の名前を入れて保存</t>
+  </si>
+  <si>
+    <t>② 注文を下へ書き足していく（納品日・品名・数量（kg）・備考）</t>
+  </si>
+  <si>
+    <t>③ 印刷して、今まで通り FAX（03-3637-8501）へ</t>
+  </si>
+  <si>
+    <t>・品名と備考は ▼ から選べます。リストに無い物も、そのまま書いてOKです</t>
+  </si>
+  <si>
+    <t>・数量は数字だけ（kg は自動で付きます）</t>
+  </si>
+  <si>
+    <t>・切り方を書かなければ、当社の規定の切り方で納品します（「切り方と商品名の一覧表」）</t>
+  </si>
+  <si>
+    <t>・g指定切りは、備考に「60g×20枚」のように</t>
+  </si>
+  <si>
+    <t>・シューマイ・ギョウザ・ワンタンの皮は、数量は空けて、備考に「160枚以上」のように</t>
+  </si>
+  <si>
+    <t>株式会社若林商店　FAX 03-3637-8501</t>
   </si>
 </sst>
 </file>
@@ -541,7 +397,7 @@
     <numFmt numFmtId="178" formatCode="yyyy&quot;年&quot;m&quot;月分&quot;"/>
     <numFmt numFmtId="179" formatCode="General&quot; kg&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,6 +513,24 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -714,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -805,6 +679,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1121,16 +997,17 @@
   <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="36.453125" style="12" customWidth="1"/>
-    <col min="3" max="4" width="18.1796875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="17.6328125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="12" customWidth="1"/>
     <col min="5" max="16384" width="8.7265625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
       <c r="B1" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>0</v>
@@ -1152,11 +1029,11 @@
     </row>
     <row r="3" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3" s="32"/>
       <c r="E3" s="9"/>
@@ -1184,7 +1061,7 @@
     </row>
     <row r="6" spans="1:5" ht="48.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>2</v>
@@ -1392,6 +1269,11 @@
       <formula>ISNUMBER($B$1)</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数量は数字だけ入れてください（kg は自動で付きます）" sqref="C7:C22" xr:uid="{76A84F07-3A7A-4DA5-80EA-509717C0408B}">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -1456,10 +1338,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1474,17 +1356,17 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1494,17 +1376,17 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1524,7 +1406,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -1549,22 +1431,22 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
@@ -1574,7 +1456,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
@@ -1584,7 +1466,7 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
@@ -1594,7 +1476,7 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
@@ -1604,7 +1486,7 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
@@ -1619,17 +1501,17 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
@@ -1644,52 +1526,52 @@
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
@@ -1699,12 +1581,12 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
@@ -1714,12 +1596,12 @@
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
@@ -1877,80 +1759,80 @@
         <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -2226,57 +2108,57 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25046304-64E5-4F5F-B5FE-0FABAA79331A}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>91</v>
+    <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A2" s="37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="14" x14ac:dyDescent="0.2">
+      <c r="A4" s="37" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -2299,7 +2181,7 @@
         <v>46311</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">

--- a/chumonsho_A4.xlsx
+++ b/chumonsho_A4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahono\Documents\株式会社若林商店\発注書書き方マニュアル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF23AB2-27F1-4A8A-8F75-6E2E5C925C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FF8FB3-67E9-4610-BABB-708244A3925B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,6 +666,8 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
@@ -679,8 +681,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -997,10 +997,9 @@
   <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="32.6328125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="13.08984375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="36.453125" style="12" customWidth="1"/>
+    <col min="3" max="4" width="18.1796875" style="12" customWidth="1"/>
     <col min="5" max="16384" width="8.7265625" style="12"/>
   </cols>
   <sheetData>
@@ -1019,29 +1018,29 @@
       <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" ht="39.65" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="31.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="32" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="32"/>
+      <c r="D3" s="34"/>
       <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5" ht="19.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="13"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
       <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5" s="17" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -2112,22 +2111,22 @@
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="33" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="14" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="33" t="s">
         <v>89</v>
       </c>
     </row>
